--- a/2026/DRAGO/Febrero/EXPENSAS-Febrero.xlsx
+++ b/2026/DRAGO/Febrero/EXPENSAS-Febrero.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\DRAGO\Febrero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Escritorio\rc-consorcio2025\2026\DRAGO\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C821A548-C9E3-4F53-8D6F-3EFA23619EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2777771-E29F-4178-A162-C78004F8B686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,25 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$49</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$32</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
   <si>
     <t>UF</t>
   </si>
@@ -283,28 +296,25 @@
     <t xml:space="preserve">Sueldo Sra. Gisela </t>
   </si>
   <si>
-    <t>AUMENTADOS EN 3n3r0 2025</t>
-  </si>
-  <si>
     <t>Seguro Sra. Gisela - Provisiorio</t>
   </si>
   <si>
-    <t>Nicolas - Fumigacion 25/01</t>
-  </si>
-  <si>
     <t>Vto. 13/03</t>
   </si>
   <si>
     <t>LIQUIDACIÓN EXPENSAS FEBRERO 2025</t>
   </si>
   <si>
-    <t>Pendiente articulos de limpieza de FEBRERO</t>
-  </si>
-  <si>
     <t>Período FEBRERO 2025</t>
   </si>
   <si>
     <t>Articulos de limpieza - Mes anterior</t>
+  </si>
+  <si>
+    <t>AUMENTADOS EN 3n3r0 2026</t>
+  </si>
+  <si>
+    <t>Fumigacion - Sr. Nicolas</t>
   </si>
 </sst>
 </file>
@@ -312,11 +322,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="167" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -842,9 +852,9 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -855,7 +865,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -879,7 +889,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -893,35 +903,35 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="3" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -931,12 +941,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="16" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
@@ -951,9 +961,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -961,8 +971,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="3" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="3" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -977,7 +987,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -992,22 +1002,21 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="6" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1018,43 +1027,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1069,11 +1078,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="16" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
-    <cellStyle name="Moneda" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1438,16 +1446,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H58"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.36328125" customWidth="1"/>
+    <col min="3" max="3" width="16.453125" customWidth="1"/>
+    <col min="4" max="4" width="12.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>17</v>
       </c>
@@ -1455,43 +1463,43 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3"/>
       <c r="B5" s="21"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="22" t="s">
         <v>35</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -1499,7 +1507,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -1507,75 +1515,73 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="19" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="53" t="s">
         <v>12</v>
       </c>
       <c r="B16" s="46"/>
       <c r="C16" s="84"/>
     </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="46" t="s">
         <v>49</v>
       </c>
       <c r="B17" s="54" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="128">
+      <c r="C17" s="51">
         <v>43870.01</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="12"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B18" s="55"/>
-      <c r="C18" s="128">
+      <c r="C18" s="51">
         <v>5842.51</v>
       </c>
       <c r="D18" s="38"/>
       <c r="E18" s="12"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="46" t="s">
         <v>42</v>
       </c>
       <c r="B19" s="56" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="51">
-        <v>19510.95</v>
-      </c>
+      <c r="C19" s="51"/>
       <c r="D19" s="5"/>
       <c r="E19" s="12"/>
       <c r="F19" s="14"/>
       <c r="H19" s="86"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="46" t="s">
         <v>31</v>
       </c>
       <c r="B20" s="56"/>
-      <c r="C20" s="107">
-        <v>169731.67</v>
+      <c r="C20" s="106">
+        <v>164925.28</v>
       </c>
       <c r="D20" s="38"/>
       <c r="F20" s="12"/>
       <c r="H20" s="86"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="46" t="s">
         <v>32</v>
       </c>
@@ -1588,33 +1594,31 @@
       <c r="D21" s="5"/>
       <c r="E21" s="12"/>
       <c r="H21" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="57"/>
       <c r="B22" s="58"/>
       <c r="C22" s="42">
         <f>SUM(C17:C21)</f>
-        <v>296146.14</v>
-      </c>
-      <c r="E22" s="108" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+        <v>271828.8</v>
+      </c>
+      <c r="E22" s="107"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="53" t="s">
         <v>33</v>
       </c>
       <c r="B23" s="56"/>
       <c r="C23" s="84"/>
     </row>
-    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="46" t="s">
         <v>84</v>
       </c>
       <c r="B24" s="59" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C24" s="51">
         <f>71883+71883*20%</f>
@@ -1622,9 +1626,9 @@
       </c>
       <c r="F24" s="18"/>
     </row>
-    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="46" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B25" s="59"/>
       <c r="C25" s="51">
@@ -1632,37 +1636,37 @@
       </c>
       <c r="F25" s="18"/>
     </row>
-    <row r="26" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="46" t="s">
         <v>83</v>
       </c>
       <c r="B26" s="59"/>
       <c r="C26" s="51">
-        <v>92000</v>
+        <v>80000</v>
       </c>
       <c r="F26" s="18"/>
     </row>
-    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="46" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B27" s="59"/>
-      <c r="C27" s="128">
+      <c r="C27" s="51">
         <v>48850</v>
       </c>
       <c r="F27" s="18"/>
     </row>
-    <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="46" t="s">
         <v>81</v>
       </c>
       <c r="B28" s="59"/>
-      <c r="C28" s="128">
+      <c r="C28" s="51">
         <v>8550</v>
       </c>
       <c r="F28" s="18"/>
     </row>
-    <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="46" t="s">
         <v>66</v>
       </c>
@@ -1672,60 +1676,60 @@
       <c r="E29" s="12"/>
       <c r="F29" s="18"/>
     </row>
-    <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="57"/>
       <c r="B30" s="58"/>
       <c r="C30" s="42">
         <f>SUM(C23:C29)</f>
-        <v>285659.59999999998</v>
+        <v>273659.59999999998</v>
       </c>
       <c r="F30" s="18"/>
     </row>
-    <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="49" t="s">
         <v>65</v>
       </c>
       <c r="B31" s="49"/>
       <c r="C31" s="60">
         <f>+C30+C22</f>
-        <v>581805.74</v>
+        <v>545488.39999999991</v>
       </c>
       <c r="F31" s="18"/>
     </row>
-    <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C32" s="43"/>
       <c r="F32" s="18"/>
     </row>
-    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="19" t="s">
         <v>43</v>
       </c>
       <c r="C33" s="43"/>
       <c r="F33" s="18"/>
     </row>
-    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="109"/>
-      <c r="B34" s="110"/>
+    <row r="34" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="108"/>
+      <c r="B34" s="109"/>
       <c r="C34" s="100"/>
       <c r="F34" s="18"/>
     </row>
-    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="104"/>
       <c r="B35" s="46"/>
       <c r="C35" s="51"/>
       <c r="F35" s="18"/>
     </row>
-    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="46"/>
       <c r="B36" s="46"/>
       <c r="C36" s="52"/>
       <c r="F36" s="18"/>
     </row>
-    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C37" s="44"/>
       <c r="F37" s="18"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="19" t="s">
         <v>39</v>
       </c>
@@ -1736,44 +1740,44 @@
       </c>
       <c r="E38" s="12"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="29" t="s">
         <v>14</v>
       </c>
       <c r="B40" s="29"/>
       <c r="C40" s="30">
         <f>+C38+C31</f>
-        <v>581805.74</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+        <v>545488.39999999991</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="31" t="s">
         <v>9</v>
       </c>
       <c r="B43" s="28"/>
       <c r="C43" s="33">
-        <v>-365036.71177661081</v>
+        <v>-153422.17853391077</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="27">
         <f>'prorrateo '!F13</f>
-        <v>734697.51324270002</v>
+        <v>454242.98606000002</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="12"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>80</v>
       </c>
@@ -1784,7 +1788,7 @@
       <c r="D45" s="12"/>
       <c r="E45" s="12"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>73</v>
       </c>
@@ -1795,43 +1799,43 @@
       <c r="D46" s="12"/>
       <c r="E46" s="12"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>64</v>
       </c>
       <c r="C47" s="61">
         <f>-(C31-C29)</f>
-        <v>-581805.74</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-545488.39999999991</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="31" t="s">
         <v>15</v>
       </c>
       <c r="B48" s="28"/>
       <c r="C48" s="33">
         <f>SUM(C43:C47)</f>
-        <v>-212144.93853391078</v>
+        <v>-244667.59247391066</v>
       </c>
       <c r="D48" s="6"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="15"/>
       <c r="B49" s="14"/>
       <c r="C49" s="16"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="15"/>
       <c r="B50" s="14"/>
       <c r="C50" s="16"/>
       <c r="F50" s="62"/>
     </row>
-    <row r="51" spans="1:6" ht="2.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" ht="2.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="15"/>
       <c r="B51" s="14"/>
       <c r="C51" s="16"/>
     </row>
-    <row r="52" spans="1:6" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="15.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="45" t="s">
         <v>60</v>
       </c>
@@ -1840,12 +1844,12 @@
         <v>109834.99657000002</v>
       </c>
     </row>
-    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="46"/>
       <c r="B53" s="46"/>
       <c r="C53" s="50"/>
     </row>
-    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="49" t="s">
         <v>4</v>
       </c>
@@ -1855,22 +1859,22 @@
         <v>109834.99657000002</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="14"/>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="14"/>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="14"/>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="14"/>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
@@ -1895,36 +1899,36 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.36328125" style="1" customWidth="1"/>
     <col min="2" max="2" width="8" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.44140625" customWidth="1"/>
-    <col min="10" max="10" width="9.109375" customWidth="1"/>
-    <col min="11" max="12" width="12.44140625" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" style="17"/>
+    <col min="3" max="3" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.36328125" customWidth="1"/>
+    <col min="6" max="6" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.453125" customWidth="1"/>
+    <col min="8" max="8" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.453125" customWidth="1"/>
+    <col min="10" max="10" width="9.08984375" customWidth="1"/>
+    <col min="11" max="12" width="12.453125" customWidth="1"/>
+    <col min="13" max="13" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.453125" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="40" t="s">
         <v>47</v>
       </c>
       <c r="E1" s="102">
-        <v>523082.98</v>
+        <v>545488.39999999991</v>
       </c>
       <c r="G1" t="str">
         <f>'detalle y gastos'!C7</f>
         <v>Vto. 13/03</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" s="71" t="str">
         <f>'detalle y gastos'!B7</f>
         <v>LIQUIDACIÓN EXPENSAS FEBRERO 2025</v>
@@ -1944,61 +1948,61 @@
       <c r="L2" s="66"/>
       <c r="M2" s="67"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="114"/>
-      <c r="B3" s="112" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A3" s="120"/>
+      <c r="B3" s="117" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="120" t="s">
+      <c r="C3" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="121" t="s">
+      <c r="D3" s="115" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="112" t="s">
+      <c r="E3" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="118" t="s">
+      <c r="F3" s="112" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="120" t="s">
+      <c r="G3" s="114" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="118" t="s">
+      <c r="H3" s="112" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="120" t="s">
+      <c r="I3" s="114" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="122" t="s">
+      <c r="J3" s="116" t="s">
         <v>77</v>
       </c>
-      <c r="K3" s="116" t="s">
+      <c r="K3" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="L3" s="116" t="s">
+      <c r="L3" s="110" t="s">
         <v>68</v>
       </c>
-      <c r="M3" s="116" t="s">
+      <c r="M3" s="110" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="115"/>
-      <c r="B4" s="113"/>
-      <c r="C4" s="120"/>
-      <c r="D4" s="121"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="122"/>
-      <c r="K4" s="117"/>
-      <c r="L4" s="117"/>
-      <c r="M4" s="117"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A4" s="121"/>
+      <c r="B4" s="118"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="111"/>
+      <c r="L4" s="111"/>
+      <c r="M4" s="111"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="68">
         <v>1</v>
       </c>
@@ -2012,15 +2016,14 @@
         <v>58</v>
       </c>
       <c r="E5" s="37">
-        <v>79281.569179999991</v>
+        <v>63293.040579999993</v>
       </c>
       <c r="F5" s="85">
-        <f>E5</f>
-        <v>79281.569179999991</v>
+        <v>63500</v>
       </c>
       <c r="G5" s="37">
         <f>E5-F5</f>
-        <v>0</v>
+        <v>-206.9594200000065</v>
       </c>
       <c r="H5" s="37">
         <f>IF(G5&gt;0,G5*3%,0)</f>
@@ -2032,18 +2035,18 @@
       <c r="J5" s="63"/>
       <c r="K5" s="75">
         <f>E1*I5</f>
-        <v>63293.040579999993</v>
+        <v>66004.09639999998</v>
       </c>
       <c r="L5" s="75">
         <f>E5-F5+H5+K5+J5</f>
-        <v>63293.040579999993</v>
+        <v>65797.136979999981</v>
       </c>
       <c r="M5" s="76">
         <f>L5+L5*4%</f>
-        <v>65824.762203199993</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+        <v>68429.022459199987</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="68">
         <v>2</v>
       </c>
@@ -2057,11 +2060,11 @@
         <v>59</v>
       </c>
       <c r="E6" s="37">
-        <v>77349.606300000014</v>
+        <v>63816.123559999993</v>
       </c>
       <c r="F6" s="85">
         <f>E6</f>
-        <v>77349.606300000014</v>
+        <v>63816.123559999993</v>
       </c>
       <c r="G6" s="37">
         <f t="shared" ref="G6:G12" si="0">E6-F6</f>
@@ -2077,20 +2080,20 @@
       <c r="J6" s="63"/>
       <c r="K6" s="75">
         <f>E1*I6</f>
-        <v>63816.123559999993</v>
+        <v>66549.584799999982</v>
       </c>
       <c r="L6" s="75">
         <f t="shared" ref="L6:L12" si="2">E6-F6+H6+K6+J6</f>
-        <v>63816.123559999993</v>
+        <v>66549.584799999982</v>
       </c>
       <c r="M6" s="76">
         <f t="shared" ref="M6:M12" si="3">L6+L6*4%</f>
-        <v>66368.768502399995</v>
+        <v>69211.568191999977</v>
       </c>
       <c r="O6" s="83"/>
       <c r="Q6" s="82"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="68">
         <v>3</v>
       </c>
@@ -2104,11 +2107,11 @@
         <v>70</v>
       </c>
       <c r="E7" s="37">
-        <v>76660.690860000002</v>
+        <v>61200.708660000004</v>
       </c>
       <c r="F7" s="85">
         <f>E7</f>
-        <v>76660.690860000002</v>
+        <v>61200.708660000004</v>
       </c>
       <c r="G7" s="37">
         <f t="shared" si="0"/>
@@ -2124,18 +2127,18 @@
       <c r="J7" s="63"/>
       <c r="K7" s="75">
         <f>E1*I7</f>
-        <v>61200.708660000004</v>
+        <v>63822.142799999994</v>
       </c>
       <c r="L7" s="75">
         <f t="shared" si="2"/>
-        <v>61200.708660000004</v>
+        <v>63822.142799999994</v>
       </c>
       <c r="M7" s="76">
         <f t="shared" si="3"/>
-        <v>63648.737006400006</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+        <v>66375.02851199999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="68">
         <v>4</v>
       </c>
@@ -2149,11 +2152,11 @@
         <v>72</v>
       </c>
       <c r="E8" s="85">
-        <v>76660.330860000002</v>
-      </c>
-      <c r="F8" s="106">
+        <v>61200.708660000004</v>
+      </c>
+      <c r="F8" s="85">
         <f>E8</f>
-        <v>76660.330860000002</v>
+        <v>61200.708660000004</v>
       </c>
       <c r="G8" s="37">
         <f t="shared" si="0"/>
@@ -2169,21 +2172,21 @@
       <c r="J8" s="63"/>
       <c r="K8" s="75">
         <f>E1*I8</f>
-        <v>61200.708660000004</v>
+        <v>63822.142799999994</v>
       </c>
       <c r="L8" s="75">
         <f t="shared" si="2"/>
-        <v>61200.708660000004</v>
+        <v>63822.142799999994</v>
       </c>
       <c r="M8" s="76">
         <f t="shared" si="3"/>
-        <v>63648.737006400006</v>
+        <v>66375.02851199999</v>
       </c>
       <c r="N8" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="68">
         <v>5</v>
       </c>
@@ -2197,11 +2200,11 @@
         <v>57</v>
       </c>
       <c r="E9" s="37">
-        <v>98502.429382700022</v>
+        <v>71662.368260000003</v>
       </c>
       <c r="F9" s="85">
         <f>E9</f>
-        <v>98502.429382700022</v>
+        <v>71662.368260000003</v>
       </c>
       <c r="G9" s="37">
         <f t="shared" si="0"/>
@@ -2217,18 +2220,18 @@
       <c r="J9" s="63"/>
       <c r="K9" s="75">
         <f>E1*I9</f>
-        <v>71662.368260000003</v>
+        <v>74731.910799999998</v>
       </c>
       <c r="L9" s="75">
         <f t="shared" si="2"/>
-        <v>71662.368260000003</v>
+        <v>74731.910799999998</v>
       </c>
       <c r="M9" s="76">
         <f t="shared" si="3"/>
-        <v>74528.862990399997</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+        <v>77721.187231999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="68">
         <v>6</v>
       </c>
@@ -2242,18 +2245,16 @@
         <v>74</v>
       </c>
       <c r="E10" s="37">
-        <v>235036.55106847221</v>
-      </c>
-      <c r="F10" s="85">
-        <v>156489</v>
-      </c>
+        <v>149950.93096052637</v>
+      </c>
+      <c r="F10" s="85"/>
       <c r="G10" s="37">
         <f t="shared" si="0"/>
-        <v>78547.55106847221</v>
+        <v>149950.93096052637</v>
       </c>
       <c r="H10" s="37">
         <f t="shared" si="1"/>
-        <v>2356.4265320541663</v>
+        <v>4498.5279288157908</v>
       </c>
       <c r="I10" s="74">
         <v>0.13200000000000001</v>
@@ -2261,18 +2262,18 @@
       <c r="J10" s="63"/>
       <c r="K10" s="75">
         <f>E1*I10</f>
-        <v>69046.95336</v>
+        <v>72004.468799999988</v>
       </c>
       <c r="L10" s="75">
         <f t="shared" si="2"/>
-        <v>149950.93096052637</v>
+        <v>226453.92768934212</v>
       </c>
       <c r="M10" s="76">
         <f t="shared" si="3"/>
-        <v>155948.96819894743</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+        <v>235512.08479691579</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="68">
         <v>7</v>
       </c>
@@ -2286,11 +2287,11 @@
         <v>56</v>
       </c>
       <c r="E11" s="37">
-        <v>86541</v>
+        <v>66431.538459999996</v>
       </c>
       <c r="F11" s="85">
         <f>E11</f>
-        <v>86541</v>
+        <v>66431.538459999996</v>
       </c>
       <c r="G11" s="37">
         <f t="shared" si="0"/>
@@ -2306,18 +2307,18 @@
       <c r="J11" s="63"/>
       <c r="K11" s="75">
         <f>E1*I11</f>
-        <v>66431.538459999996</v>
+        <v>69277.026799999992</v>
       </c>
       <c r="L11" s="75">
         <f t="shared" si="2"/>
-        <v>66431.538459999996</v>
+        <v>69277.026799999992</v>
       </c>
       <c r="M11" s="76">
         <f t="shared" si="3"/>
-        <v>69088.799998399991</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+        <v>72048.107871999993</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="68">
         <v>8</v>
       </c>
@@ -2331,11 +2332,11 @@
         <v>55</v>
       </c>
       <c r="E12" s="37">
-        <v>83212.886659999989</v>
+        <v>66431.538459999996</v>
       </c>
       <c r="F12" s="85">
         <f>E12</f>
-        <v>83212.886659999989</v>
+        <v>66431.538459999996</v>
       </c>
       <c r="G12" s="37">
         <f t="shared" si="0"/>
@@ -2351,18 +2352,18 @@
       <c r="J12" s="63"/>
       <c r="K12" s="75">
         <f>E1*I12</f>
-        <v>66431.538459999996</v>
+        <v>69277.026799999992</v>
       </c>
       <c r="L12" s="75">
         <f t="shared" si="2"/>
-        <v>66431.538459999996</v>
+        <v>69277.026799999992</v>
       </c>
       <c r="M12" s="76">
         <f t="shared" si="3"/>
-        <v>69088.799998399991</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>72048.107871999993</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="77" t="s">
         <v>10</v>
       </c>
@@ -2371,16 +2372,16 @@
       <c r="D13" s="79"/>
       <c r="E13" s="80">
         <f>SUM(E5:E12)</f>
-        <v>813245.06431117223</v>
+        <v>603986.95760052628</v>
       </c>
       <c r="F13" s="69">
         <f>SUM(F5:F12)</f>
-        <v>734697.51324270002</v>
+        <v>454242.98606000002</v>
       </c>
       <c r="G13" s="69"/>
       <c r="H13" s="69">
         <f>SUM(H5:H12)</f>
-        <v>2356.4265320541663</v>
+        <v>4498.5279288157908</v>
       </c>
       <c r="I13" s="70">
         <f t="shared" ref="I13" si="4">SUM(I5:I12)</f>
@@ -2392,350 +2393,355 @@
       </c>
       <c r="K13" s="80">
         <f>SUM(K5:K12)</f>
-        <v>523082.98</v>
+        <v>545488.39999999991</v>
       </c>
       <c r="L13" s="80">
         <f>SUM(L5:L12)</f>
-        <v>603986.95760052628</v>
+        <v>699730.89946934208</v>
       </c>
       <c r="M13" s="81">
         <f>SUM(M5:M12)</f>
-        <v>628146.43590454746</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C15" s="111" t="s">
+        <v>727720.13544811564</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="C15" s="119" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="111"/>
-      <c r="E15" s="111"/>
-      <c r="F15" s="111"/>
-      <c r="G15" s="111"/>
-      <c r="H15" s="111"/>
-      <c r="I15" s="111"/>
-      <c r="J15" s="111"/>
-      <c r="K15" s="111"/>
-      <c r="L15" s="111"/>
-    </row>
-    <row r="16" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D15" s="119"/>
+      <c r="E15" s="119"/>
+      <c r="F15" s="119"/>
+      <c r="G15" s="119"/>
+      <c r="H15" s="119"/>
+      <c r="I15" s="119"/>
+      <c r="J15" s="119"/>
+      <c r="K15" s="119"/>
+      <c r="L15" s="119"/>
+    </row>
+    <row r="16" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="111"/>
-      <c r="D16" s="111"/>
-      <c r="E16" s="111"/>
-      <c r="F16" s="111"/>
-      <c r="G16" s="111"/>
-      <c r="H16" s="111"/>
-      <c r="I16" s="111"/>
-      <c r="J16" s="111"/>
-      <c r="K16" s="111"/>
-      <c r="L16" s="111"/>
-    </row>
-    <row r="17" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="119"/>
+      <c r="D16" s="119"/>
+      <c r="E16" s="119"/>
+      <c r="F16" s="119"/>
+      <c r="G16" s="119"/>
+      <c r="H16" s="119"/>
+      <c r="I16" s="119"/>
+      <c r="J16" s="119"/>
+      <c r="K16" s="119"/>
+      <c r="L16" s="119"/>
+    </row>
+    <row r="17" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="24" t="s">
         <v>50</v>
       </c>
       <c r="B17" s="25"/>
-      <c r="C17" s="111"/>
-      <c r="D17" s="111"/>
-      <c r="E17" s="111"/>
-      <c r="F17" s="111"/>
-      <c r="G17" s="111"/>
-      <c r="H17" s="111"/>
-      <c r="I17" s="111"/>
-      <c r="J17" s="111"/>
-      <c r="K17" s="111"/>
-      <c r="L17" s="111"/>
+      <c r="C17" s="119"/>
+      <c r="D17" s="119"/>
+      <c r="E17" s="119"/>
+      <c r="F17" s="119"/>
+      <c r="G17" s="119"/>
+      <c r="H17" s="119"/>
+      <c r="I17" s="119"/>
+      <c r="J17" s="119"/>
+      <c r="K17" s="119"/>
+      <c r="L17" s="119"/>
       <c r="M17" s="26"/>
     </row>
-    <row r="18" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="111"/>
-      <c r="D18" s="111"/>
-      <c r="E18" s="111"/>
-      <c r="F18" s="111"/>
-      <c r="G18" s="111"/>
-      <c r="H18" s="111"/>
-      <c r="I18" s="111"/>
-      <c r="J18" s="111"/>
-      <c r="K18" s="111"/>
-      <c r="L18" s="111"/>
+      <c r="C18" s="119"/>
+      <c r="D18" s="119"/>
+      <c r="E18" s="119"/>
+      <c r="F18" s="119"/>
+      <c r="G18" s="119"/>
+      <c r="H18" s="119"/>
+      <c r="I18" s="119"/>
+      <c r="J18" s="119"/>
+      <c r="K18" s="119"/>
+      <c r="L18" s="119"/>
       <c r="M18" s="36" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2"/>
       <c r="B19" s="7"/>
-      <c r="C19" s="111"/>
-      <c r="D19" s="111"/>
-      <c r="E19" s="111"/>
-      <c r="F19" s="111"/>
-      <c r="G19" s="111"/>
-      <c r="H19" s="111"/>
-      <c r="I19" s="111"/>
-      <c r="J19" s="111"/>
-      <c r="K19" s="111"/>
-      <c r="L19" s="111"/>
+      <c r="C19" s="119"/>
+      <c r="D19" s="119"/>
+      <c r="E19" s="119"/>
+      <c r="F19" s="119"/>
+      <c r="G19" s="119"/>
+      <c r="H19" s="119"/>
+      <c r="I19" s="119"/>
+      <c r="J19" s="119"/>
+      <c r="K19" s="119"/>
+      <c r="L19" s="119"/>
       <c r="M19" s="32" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="10">
         <v>1</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="111"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="111"/>
-      <c r="F20" s="111"/>
-      <c r="G20" s="111"/>
-      <c r="H20" s="111"/>
-      <c r="I20" s="111"/>
-      <c r="J20" s="111"/>
-      <c r="K20" s="111"/>
-      <c r="L20" s="111"/>
+      <c r="C20" s="119"/>
+      <c r="D20" s="119"/>
+      <c r="E20" s="119"/>
+      <c r="F20" s="119"/>
+      <c r="G20" s="119"/>
+      <c r="H20" s="119"/>
+      <c r="I20" s="119"/>
+      <c r="J20" s="119"/>
+      <c r="K20" s="119"/>
+      <c r="L20" s="119"/>
       <c r="M20" s="34" t="e">
         <f>+#REF!+H20+K20</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="10">
         <v>2</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="111"/>
-      <c r="D21" s="111"/>
-      <c r="E21" s="111"/>
-      <c r="F21" s="111"/>
-      <c r="G21" s="111"/>
-      <c r="H21" s="111"/>
-      <c r="I21" s="111"/>
-      <c r="J21" s="111"/>
-      <c r="K21" s="111"/>
-      <c r="L21" s="111"/>
+      <c r="C21" s="119"/>
+      <c r="D21" s="119"/>
+      <c r="E21" s="119"/>
+      <c r="F21" s="119"/>
+      <c r="G21" s="119"/>
+      <c r="H21" s="119"/>
+      <c r="I21" s="119"/>
+      <c r="J21" s="119"/>
+      <c r="K21" s="119"/>
+      <c r="L21" s="119"/>
       <c r="M21" s="34" t="e">
         <f>+#REF!+H21+K21</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="10">
         <v>3</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="111"/>
-      <c r="D22" s="111"/>
-      <c r="E22" s="111"/>
-      <c r="F22" s="111"/>
-      <c r="G22" s="111"/>
-      <c r="H22" s="111"/>
-      <c r="I22" s="111"/>
-      <c r="J22" s="111"/>
-      <c r="K22" s="111"/>
-      <c r="L22" s="111"/>
+      <c r="C22" s="119"/>
+      <c r="D22" s="119"/>
+      <c r="E22" s="119"/>
+      <c r="F22" s="119"/>
+      <c r="G22" s="119"/>
+      <c r="H22" s="119"/>
+      <c r="I22" s="119"/>
+      <c r="J22" s="119"/>
+      <c r="K22" s="119"/>
+      <c r="L22" s="119"/>
       <c r="M22" s="34" t="e">
         <f>+#REF!+H22+K22</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="10">
         <v>4</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="111"/>
-      <c r="D23" s="111"/>
-      <c r="E23" s="111"/>
-      <c r="F23" s="111"/>
-      <c r="G23" s="111"/>
-      <c r="H23" s="111"/>
-      <c r="I23" s="111"/>
-      <c r="J23" s="111"/>
-      <c r="K23" s="111"/>
-      <c r="L23" s="111"/>
+      <c r="C23" s="119"/>
+      <c r="D23" s="119"/>
+      <c r="E23" s="119"/>
+      <c r="F23" s="119"/>
+      <c r="G23" s="119"/>
+      <c r="H23" s="119"/>
+      <c r="I23" s="119"/>
+      <c r="J23" s="119"/>
+      <c r="K23" s="119"/>
+      <c r="L23" s="119"/>
       <c r="M23" s="34" t="e">
         <f>+#REF!+H23+K23</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="10">
         <v>5</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="111"/>
-      <c r="D24" s="111"/>
-      <c r="E24" s="111"/>
-      <c r="F24" s="111"/>
-      <c r="G24" s="111"/>
-      <c r="H24" s="111"/>
-      <c r="I24" s="111"/>
-      <c r="J24" s="111"/>
-      <c r="K24" s="111"/>
-      <c r="L24" s="111"/>
+      <c r="C24" s="119"/>
+      <c r="D24" s="119"/>
+      <c r="E24" s="119"/>
+      <c r="F24" s="119"/>
+      <c r="G24" s="119"/>
+      <c r="H24" s="119"/>
+      <c r="I24" s="119"/>
+      <c r="J24" s="119"/>
+      <c r="K24" s="119"/>
+      <c r="L24" s="119"/>
       <c r="M24" s="34" t="e">
         <f>+#REF!+H24+K24</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="10">
         <v>6</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="111"/>
-      <c r="D25" s="111"/>
-      <c r="E25" s="111"/>
-      <c r="F25" s="111"/>
-      <c r="G25" s="111"/>
-      <c r="H25" s="111"/>
-      <c r="I25" s="111"/>
-      <c r="J25" s="111"/>
-      <c r="K25" s="111"/>
-      <c r="L25" s="111"/>
+      <c r="C25" s="119"/>
+      <c r="D25" s="119"/>
+      <c r="E25" s="119"/>
+      <c r="F25" s="119"/>
+      <c r="G25" s="119"/>
+      <c r="H25" s="119"/>
+      <c r="I25" s="119"/>
+      <c r="J25" s="119"/>
+      <c r="K25" s="119"/>
+      <c r="L25" s="119"/>
       <c r="M25" s="34" t="e">
         <f>+#REF!+H25+K25</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="10">
         <v>7</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="111"/>
-      <c r="D26" s="111"/>
-      <c r="E26" s="111"/>
-      <c r="F26" s="111"/>
-      <c r="G26" s="111"/>
-      <c r="H26" s="111"/>
-      <c r="I26" s="111"/>
-      <c r="J26" s="111"/>
-      <c r="K26" s="111"/>
-      <c r="L26" s="111"/>
+      <c r="C26" s="119"/>
+      <c r="D26" s="119"/>
+      <c r="E26" s="119"/>
+      <c r="F26" s="119"/>
+      <c r="G26" s="119"/>
+      <c r="H26" s="119"/>
+      <c r="I26" s="119"/>
+      <c r="J26" s="119"/>
+      <c r="K26" s="119"/>
+      <c r="L26" s="119"/>
       <c r="M26" s="34" t="e">
         <f>+#REF!+H26+K26</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10">
         <v>8</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="111"/>
-      <c r="D27" s="111"/>
-      <c r="E27" s="111"/>
-      <c r="F27" s="111"/>
-      <c r="G27" s="111"/>
-      <c r="H27" s="111"/>
-      <c r="I27" s="111"/>
-      <c r="J27" s="111"/>
-      <c r="K27" s="111"/>
-      <c r="L27" s="111"/>
+      <c r="C27" s="119"/>
+      <c r="D27" s="119"/>
+      <c r="E27" s="119"/>
+      <c r="F27" s="119"/>
+      <c r="G27" s="119"/>
+      <c r="H27" s="119"/>
+      <c r="I27" s="119"/>
+      <c r="J27" s="119"/>
+      <c r="K27" s="119"/>
+      <c r="L27" s="119"/>
       <c r="M27" s="34" t="e">
         <f>+#REF!+H27+K27</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="8" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="9"/>
-      <c r="C28" s="111"/>
-      <c r="D28" s="111"/>
-      <c r="E28" s="111"/>
-      <c r="F28" s="111"/>
-      <c r="G28" s="111"/>
-      <c r="H28" s="111"/>
-      <c r="I28" s="111"/>
-      <c r="J28" s="111"/>
-      <c r="K28" s="111"/>
-      <c r="L28" s="111"/>
+      <c r="C28" s="119"/>
+      <c r="D28" s="119"/>
+      <c r="E28" s="119"/>
+      <c r="F28" s="119"/>
+      <c r="G28" s="119"/>
+      <c r="H28" s="119"/>
+      <c r="I28" s="119"/>
+      <c r="J28" s="119"/>
+      <c r="K28" s="119"/>
+      <c r="L28" s="119"/>
       <c r="M28" s="35" t="e">
         <f>SUM(M20:M27)</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C29" s="111"/>
-      <c r="D29" s="111"/>
-      <c r="E29" s="111"/>
-      <c r="F29" s="111"/>
-      <c r="G29" s="111"/>
-      <c r="H29" s="111"/>
-      <c r="I29" s="111"/>
-      <c r="J29" s="111"/>
-      <c r="K29" s="111"/>
-      <c r="L29" s="111"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C30" s="111"/>
-      <c r="D30" s="111"/>
-      <c r="E30" s="111"/>
-      <c r="F30" s="111"/>
-      <c r="G30" s="111"/>
-      <c r="H30" s="111"/>
-      <c r="I30" s="111"/>
-      <c r="J30" s="111"/>
-      <c r="K30" s="111"/>
-      <c r="L30" s="111"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C31" s="111"/>
-      <c r="D31" s="111"/>
-      <c r="E31" s="111"/>
-      <c r="F31" s="111"/>
-      <c r="G31" s="111"/>
-      <c r="H31" s="111"/>
-      <c r="I31" s="111"/>
-      <c r="J31" s="111"/>
-      <c r="K31" s="111"/>
-      <c r="L31" s="111"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C32" s="111"/>
-      <c r="D32" s="111"/>
-      <c r="E32" s="111"/>
-      <c r="F32" s="111"/>
-      <c r="G32" s="111"/>
-      <c r="H32" s="111"/>
-      <c r="I32" s="111"/>
-      <c r="J32" s="111"/>
-      <c r="K32" s="111"/>
-      <c r="L32" s="111"/>
-    </row>
-    <row r="39" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C29" s="119"/>
+      <c r="D29" s="119"/>
+      <c r="E29" s="119"/>
+      <c r="F29" s="119"/>
+      <c r="G29" s="119"/>
+      <c r="H29" s="119"/>
+      <c r="I29" s="119"/>
+      <c r="J29" s="119"/>
+      <c r="K29" s="119"/>
+      <c r="L29" s="119"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C30" s="119"/>
+      <c r="D30" s="119"/>
+      <c r="E30" s="119"/>
+      <c r="F30" s="119"/>
+      <c r="G30" s="119"/>
+      <c r="H30" s="119"/>
+      <c r="I30" s="119"/>
+      <c r="J30" s="119"/>
+      <c r="K30" s="119"/>
+      <c r="L30" s="119"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C31" s="119"/>
+      <c r="D31" s="119"/>
+      <c r="E31" s="119"/>
+      <c r="F31" s="119"/>
+      <c r="G31" s="119"/>
+      <c r="H31" s="119"/>
+      <c r="I31" s="119"/>
+      <c r="J31" s="119"/>
+      <c r="K31" s="119"/>
+      <c r="L31" s="119"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C32" s="119"/>
+      <c r="D32" s="119"/>
+      <c r="E32" s="119"/>
+      <c r="F32" s="119"/>
+      <c r="G32" s="119"/>
+      <c r="H32" s="119"/>
+      <c r="I32" s="119"/>
+      <c r="J32" s="119"/>
+      <c r="K32" s="119"/>
+      <c r="L32" s="119"/>
+    </row>
+    <row r="39" spans="5:5" x14ac:dyDescent="0.35">
       <c r="E39" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="C15:L32"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="F3:F4"/>
@@ -2745,11 +2751,6 @@
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="C15:L32"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2760,29 +2761,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" customWidth="1"/>
-    <col min="5" max="5" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.109375" customWidth="1"/>
+    <col min="1" max="1" width="6.36328125" customWidth="1"/>
+    <col min="3" max="3" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.36328125" customWidth="1"/>
+    <col min="5" max="5" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.08984375" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="11.109375" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" customWidth="1"/>
+    <col min="8" max="8" width="11.08984375" customWidth="1"/>
+    <col min="9" max="9" width="14.6328125" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="91" t="s">
         <v>48</v>
       </c>
       <c r="B1" s="92"/>
       <c r="C1" s="93"/>
-      <c r="D1" s="123">
-        <v>0</v>
-      </c>
-      <c r="E1" s="123"/>
+      <c r="D1" s="122">
+        <v>0</v>
+      </c>
+      <c r="E1" s="122"/>
       <c r="F1" s="103"/>
       <c r="G1" s="93"/>
       <c r="H1" s="93"/>
@@ -2790,7 +2791,7 @@
       <c r="J1" s="94"/>
       <c r="L1" s="17"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="95" t="s">
         <v>76</v>
       </c>
@@ -2807,53 +2808,53 @@
       <c r="J2" s="96"/>
       <c r="L2" s="17"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="124" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="112" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="123" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="117" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="112" t="s">
+      <c r="C3" s="117" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="121" t="s">
+      <c r="D3" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="120" t="s">
+      <c r="E3" s="114" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="112" t="s">
+      <c r="F3" s="117" t="s">
         <v>79</v>
       </c>
-      <c r="G3" s="121" t="s">
+      <c r="G3" s="115" t="s">
         <v>44</v>
       </c>
-      <c r="H3" s="120" t="s">
+      <c r="H3" s="114" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="127" t="s">
+      <c r="I3" s="126" t="s">
         <v>75</v>
       </c>
-      <c r="J3" s="126" t="s">
+      <c r="J3" s="125" t="s">
         <v>53</v>
       </c>
       <c r="L3" s="17"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="125"/>
-      <c r="B4" s="113"/>
-      <c r="C4" s="113"/>
-      <c r="D4" s="121"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="127"/>
-      <c r="J4" s="126"/>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="124"/>
+      <c r="B4" s="118"/>
+      <c r="C4" s="118"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="126"/>
+      <c r="J4" s="125"/>
       <c r="L4" s="17"/>
     </row>
-    <row r="5" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="98">
         <v>1</v>
       </c>
@@ -2890,7 +2891,7 @@
       </c>
       <c r="L5" s="17"/>
     </row>
-    <row r="6" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="98">
         <v>2</v>
       </c>
@@ -2927,7 +2928,7 @@
       </c>
       <c r="L6" s="17"/>
     </row>
-    <row r="7" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="98">
         <v>3</v>
       </c>
@@ -2965,7 +2966,7 @@
       </c>
       <c r="L7" s="17"/>
     </row>
-    <row r="8" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="98">
         <v>4</v>
       </c>
@@ -3002,7 +3003,7 @@
       </c>
       <c r="L8" s="17"/>
     </row>
-    <row r="9" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="98">
         <v>5</v>
       </c>
@@ -3039,7 +3040,7 @@
       </c>
       <c r="L9" s="17"/>
     </row>
-    <row r="10" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="98">
         <v>6</v>
       </c>
@@ -3076,7 +3077,7 @@
       </c>
       <c r="L10" s="17"/>
     </row>
-    <row r="11" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="98">
         <v>7</v>
       </c>
@@ -3114,7 +3115,7 @@
       </c>
       <c r="L11" s="17"/>
     </row>
-    <row r="12" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="98">
         <v>8</v>
       </c>
@@ -3152,7 +3153,7 @@
       </c>
       <c r="L12" s="17"/>
     </row>
-    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="77" t="s">
         <v>10</v>
       </c>
